--- a/Result/profitability/6242.xlsx
+++ b/Result/profitability/6242.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.21</v>
       </c>
       <c r="M2" t="n">
-        <v>0.39125</v>
+        <v>0.42</v>
       </c>
       <c r="N2" t="n">
-        <v>61.28874999999999</v>
+        <v>61.16375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.25</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1675</v>
+        <v>0.15875</v>
       </c>
       <c r="N3" t="n">
-        <v>51.2525</v>
+        <v>51.14125</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.18</v>
       </c>
       <c r="M4" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>45.5225</v>
+        <v>45.40125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.53</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.035</v>
       </c>
       <c r="N5" t="n">
-        <v>44.89375</v>
+        <v>44.81874999999999</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>-0.29</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.09749999999999999</v>
+        <v>-0.05374999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>38.09125</v>
+        <v>38.00624999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.36</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.195</v>
+        <v>-0.2075</v>
       </c>
       <c r="N7" t="n">
-        <v>32.14624999999999</v>
+        <v>32.09625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.85</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4099999999999999</v>
+        <v>-0.355</v>
       </c>
       <c r="N8" t="n">
-        <v>27.89875</v>
+        <v>27.89</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>-0.62</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4399999999999999</v>
+        <v>-0.44</v>
       </c>
       <c r="N10" t="n">
         <v>21.08875</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6242</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>162</v>
+      </c>
+      <c r="D75" t="n">
+        <v>54</v>
+      </c>
+      <c r="E75" t="n">
+        <v>108</v>
+      </c>
+      <c r="F75" t="n">
+        <v>66.95</v>
+      </c>
+      <c r="G75" t="n">
+        <v>27</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>16.70%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="n">
+        <v>29</v>
+      </c>
+      <c r="K75" t="n">
+        <v>25</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.6387499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>67.52624999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.333333333333333</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.06999999999999318</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.001044464339003182</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.04000000000000004</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.04938271604938271</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.5999999999999943</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.008882309400443988</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
